--- a/results/Int Task Remove ACC 0.4/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_6_permute.xlsx
@@ -440,23 +440,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8532915360501567</v>
+        <v>0.850096455268869</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8481673498914879</v>
+        <v>0.8513142030383409</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -466,451 +466,451 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8572703158910056</v>
+        <v>0.8562937062937064</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8548348203520617</v>
+        <v>0.8610682421027248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8542319749216301</v>
+        <v>0.8619122257053291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.855449722691102</v>
+        <v>0.8605859657583795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8586206896551725</v>
+        <v>0.8605859657583795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8613093802748975</v>
+        <v>0.8599228357849047</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8583433807571739</v>
+        <v>0.8579334458644803</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8583433807571739</v>
+        <v>0.8586327465637811</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8563901615625753</v>
+        <v>0.8576923076923078</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8502531950807812</v>
+        <v>0.8596816976127322</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.85617313720762</v>
+        <v>0.7184711839884254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8588256571015191</v>
+        <v>0.7184711839884254</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8572944297082228</v>
+        <v>0.7122618760549795</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8686761514347721</v>
+        <v>0.706534844465879</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8712563298770195</v>
+        <v>0.7030021702435496</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8702797202797202</v>
+        <v>0.7003858210754763</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8745840366530022</v>
+        <v>0.6977333011815771</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.871304557511454</v>
+        <v>0.7152881601157464</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8656860380998312</v>
+        <v>0.6893899204244032</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8679768507354715</v>
+        <v>0.6827586206896552</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8367976850735471</v>
+        <v>0.6529177718832891</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8404991560163975</v>
+        <v>0.6258379551483</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8358210754762478</v>
+        <v>0.6258379551483</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8400771642150953</v>
+        <v>0.6254521340728237</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8440559440559441</v>
+        <v>0.6318061249095732</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8354352544007717</v>
+        <v>0.6206775982638051</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.846419098143236</v>
+        <v>0.6170122980467808</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8217144924041475</v>
+        <v>0.616349168073306</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.806305763202315</v>
+        <v>0.6285748734024597</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7953822040028937</v>
+        <v>0.6227152158186641</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7898721967687485</v>
+        <v>0.6203761755485894</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7836267181094767</v>
+        <v>0.6319749216300941</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7836267181094767</v>
+        <v>0.6477212442729684</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7373402459609356</v>
+        <v>0.6400289365806607</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7390161562575355</v>
+        <v>0.6303954666023631</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7043525440077164</v>
+        <v>0.4616469737159392</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.675476247890041</v>
+        <v>0.4689655172413793</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6664215095249578</v>
+        <v>0.4928864239209067</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6757294429708223</v>
+        <v>0.5507836990595611</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6762840607668195</v>
+        <v>0.5100554617795997</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.677115987460815</v>
+        <v>0.5093923318061249</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7191222570532916</v>
+        <v>0.4599348926935133</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7079213889558718</v>
+        <v>0.4599348926935133</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7158668917289607</v>
+        <v>0.4588859416445624</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7280081986978539</v>
+        <v>0.4605256812153364</v>
       </c>
     </row>
     <row r="50">
@@ -920,67 +920,67 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7306968893175789</v>
+        <v>0.4605256812153364</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.755220641427538</v>
+        <v>0.4519893899204244</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7693513383168555</v>
+        <v>0.466939956595129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7622980467808054</v>
+        <v>0.4679165661924283</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7622980467808054</v>
+        <v>0.4685073547142513</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7551482999758862</v>
+        <v>0.4650711357607909</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6259946949602122</v>
+        <v>0.4687967205208585</v>
       </c>
     </row>
     <row r="57">
@@ -990,337 +990,337 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6123824451410659</v>
+        <v>0.481022425850012</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6123824451410659</v>
+        <v>0.4803954666023632</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5621292500602846</v>
+        <v>0.4766698818422956</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.594321196045334</v>
+        <v>0.4803592958765373</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6337231733783458</v>
+        <v>0.4765975403906438</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6320834338075717</v>
+        <v>0.4765975403906438</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6438148058837714</v>
+        <v>0.4765975403906438</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6428381962864721</v>
+        <v>0.4769110200144683</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5979020979020979</v>
+        <v>0.4769110200144683</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5952134072823728</v>
+        <v>0.4827586206896552</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5367615143477212</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5351338316855558</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5790089221123704</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5615022908126357</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5418736435977816</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.541596334699783</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5324330841572221</v>
+        <v>0.4996865203761756</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5388594164456233</v>
+        <v>0.4996865203761756</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5478418133590548</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.556631299734748</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4993368700265252</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4993368700265252</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4990233904027007</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4989389920424404</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5000241138172172</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4934289848082951</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5001687967205208</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5003978779840849</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4975524475524475</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4918615866891729</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4898360260429226</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4852061731372076</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4937424644321196</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4943694236797685</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
